--- a/INSTANCES/instances_WCTR_xlsx/A_MTN_3/231FL_10A.xlsx
+++ b/INSTANCES/instances_WCTR_xlsx/A_MTN_3/231FL_10A.xlsx
@@ -7704,7 +7704,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -7721,7 +7721,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -7738,7 +7738,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -7755,7 +7755,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -7806,7 +7806,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -7823,7 +7823,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -7857,7 +7857,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>1</v>
